--- a/fixtures/workday_view_my_courses.xlsx
+++ b/fixtures/workday_view_my_courses.xlsx
@@ -413,97 +413,333 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>View My Courses</t>
+          <t>My Enrolled Courses</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Enrolled Sections</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
         <is>
           <t>Course Listing</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Drop</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Swap</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Withdraw</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Credits</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Grading Basis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Registration Status</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>Instructional Format</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Delivery Mode</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>Meeting Patterns</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Grading Basis</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Instructor</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Start Date</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>End Date</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CPSC 121 001 - Models of Computation</t>
+          <t>Jane Student (00000000) - Faculty of Fake Studies/Undergraduate - 2026-01-01 - Active - FAKE 100 - Introduction to Fake Studies</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>FAKE 100 - Introduction to Fake Studies</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Graded</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>FAKE 100 - Introduction to Fake Studies-101 - Introduction to Fake Studies</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Registered</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>Lecture</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-09-08 - 2026-12-05 | Mon Wed Fri | 10:00 A.M. - 11:00 A.M. | Lecture | Detwiler Pavilion (DMP) | Floor: 1 | Room: 110</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Graded</t>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>In Person Learning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-09-08 - 2026-12-05 | Mon Wed Fri | 10:00 a.m. - 11:00 a.m. | Fake Building (FAKE) | Floor: 1 | Room: 100</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>J. Doe</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MATH 200 201 - Calculus III</t>
+          <t>Jane Student (00000000) - Faculty of Fake Studies/Undergraduate - 2026-01-01 - Active - FAKE 100 - Introduction to Fake Studies</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lecture</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-09-08 - 2026-12-05 | Tue Thu | 9:30 A.M. - 11:00 A.M. | Lecture | Mathematics Building (MATX) | Floor: 2 | Room: 1100</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>FAKE 100 - Introduction to Fake Studies</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Graded</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>FAKE 100 - Introduction to Fake Studies-L1A - Introduction to Fake Studies</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Registered</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Laboratory</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>In Person Learning</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-09-08 - 2026-12-05 | Mon Wed Fri | 10:00 a.m. - 11:00 a.m. | Fake Building (FAKE) | Floor: 1 | Room: 100</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>J. Doe</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cpsc 210 - Software Construction</t>
+          <t>Jane Student (00000000) - Faculty of Fake Studies/Undergraduate - 2026-01-01 - Active - FAKE 200 - Advanced Fake Concepts</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>FAKE 200 - Advanced Fake Concepts</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Graded</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>FAKE 200 - Advanced Fake Concepts-201 - Advanced Fake Concepts</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Registered</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>Lecture</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>In Person Learning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-09-08 - 2026-12-05 | Mon Wed Fri | 10:00 a.m. - 11:00 a.m. | Fake Building (FAKE) | Floor: 1 | Room: 100</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>J. Doe</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Jane Student (00000000) - Faculty of Fake Studies/Undergraduate - 2026-01-01 - Active - fake300</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fake300</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>Graded</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>fake300-301</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Registered</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Lecture</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>In Person Learning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-09-08 - 2026-12-05 | Mon Wed Fri | 10:00 a.m. - 11:00 a.m. | Fake Building (FAKE) | Floor: 1 | Room: 100</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>J. Doe</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2026-12-05</t>
         </is>
       </c>
     </row>

--- a/fixtures/workday_view_my_courses.xlsx
+++ b/fixtures/workday_view_my_courses.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +48,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +434,6 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
           <t>Course Listing</t>
@@ -506,12 +508,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jane Student (00000000) - Faculty of Fake Studies/Undergraduate - 2026-01-01 - Active - FAKE 100 - Introduction to Fake Studies</t>
+          <t>Student (00000000) - School of Biomedical Engineering/Undergraduate (B.A.Sc.) - 2026-06-22 - Active - BMEG_V 210 - Thermodynamics in Biomedical Engineering - 2026-27 Winter Term 1 (UBC-V)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FAKE 100 - Introduction to Fake Studies</t>
+          <t>BMEG_V 210 - Thermodynamics in Biomedical Engineering</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -524,7 +526,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>FAKE 100 - Introduction to Fake Studies-101 - Introduction to Fake Studies</t>
+          <t>BMEG_V 210-101 - Thermodynamics in Biomedical Engineering</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -544,34 +546,30 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-09-08 - 2026-12-05 | Mon Wed Fri | 10:00 a.m. - 11:00 a.m. | Fake Building (FAKE) | Floor: 1 | Room: 100</t>
+          <t>2026-09-09 - 2026-12-07 | Mon Wed Fri | 1:00 p.m. - 2:00 p.m. | UBCV | P. A. Woodward Instructional Resources Centre (IRC) | Floor: G | Room: 5</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>J. Doe</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2026-12-05</t>
-        </is>
+          <t>Yanpu He</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O4" s="1" t="n">
+        <v>46363</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jane Student (00000000) - Faculty of Fake Studies/Undergraduate - 2026-01-01 - Active - FAKE 100 - Introduction to Fake Studies</t>
+          <t>Student (00000000) - School of Biomedical Engineering/Undergraduate (B.A.Sc.) - 2026-06-22 - Active - BMEG_V 210 - Thermodynamics in Biomedical Engineering - 2026-27 Winter Term 1 (UBC-V)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FAKE 100 - Introduction to Fake Studies</t>
+          <t>BMEG_V 210 - Thermodynamics in Biomedical Engineering</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -584,7 +582,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>FAKE 100 - Introduction to Fake Studies-L1A - Introduction to Fake Studies</t>
+          <t>BMEG_V 210-T1A - Thermodynamics in Biomedical Engineering</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -594,7 +592,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Laboratory</t>
+          <t>Discussion</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -604,38 +602,34 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-09-08 - 2026-12-05 | Mon Wed Fri | 10:00 a.m. - 11:00 a.m. | Fake Building (FAKE) | Floor: 1 | Room: 100</t>
+          <t>2026-09-11 - 2026-12-04 | Fri | 8:00 a.m. - 10:00 a.m. | UBCV | P. A. Woodward Instructional Resources Centre (IRC) | Floor: G | Room: 5</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>J. Doe</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2026-12-05</t>
-        </is>
+          <t>Yanpu He</t>
+        </is>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>46363</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jane Student (00000000) - Faculty of Fake Studies/Undergraduate - 2026-01-01 - Active - FAKE 200 - Advanced Fake Concepts</t>
+          <t>Student (00000000) - School of Biomedical Engineering/Undergraduate (B.A.Sc.) - 2026-06-22 - Active - BMEG_V 245 - The Fundamental Units of Life: From Cells To Systems - 2026-27 Winter Term 1 (UBC-V)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FAKE 200 - Advanced Fake Concepts</t>
+          <t>BMEG_V 245 - The Fundamental Units of Life: From Cells To Systems</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -644,7 +638,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>FAKE 200 - Advanced Fake Concepts-201 - Advanced Fake Concepts</t>
+          <t>BMEG_V 245-101 - The Fundamental Units of Life: From Cells To Systems</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -664,83 +658,859 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-09-08 - 2026-12-05 | Mon Wed Fri | 10:00 a.m. - 11:00 a.m. | Fake Building (FAKE) | Floor: 1 | Room: 100</t>
+          <t>2026-09-09 - 2026-12-07 | Mon Wed Fri | 10:00 a.m. - 11:00 a.m. | UBCV | P. A. Woodward Instructional Resources Centre (IRC) | Floor: G | Room: 1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>J. Doe</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2026-12-05</t>
-        </is>
+          <t>Dayag Sheykhkarimli
+Nozomu Yachie</t>
+        </is>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>46363</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jane Student (00000000) - Faculty of Fake Studies/Undergraduate - 2026-01-01 - Active - fake300</t>
+          <t>Student (00000000) - School of Biomedical Engineering/Undergraduate (B.A.Sc.) - 2026-06-22 - Active - BMEG_V 245 - The Fundamental Units of Life: From Cells To Systems - 2026-27 Winter Term 1 (UBC-V)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fake300</t>
+          <t>BMEG_V 245 - The Fundamental Units of Life: From Cells To Systems</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Graded</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>BMEG_V 245-L1D - The Fundamental Units of Life: From Cells To Systems</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Registered</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Laboratory</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>In Person Learning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-09-16 - 2026-11-25 | Wed (Alternate weeks) | 4:00 p.m. - 7:00 p.m. | UBCV | Gordon B. Shrum Building (SHRM) | Floor: 2 | Room: 2053</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Dayag Sheykhkarimli
+Nozomu Yachie</t>
+        </is>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>46363</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Student (00000000) - School of Biomedical Engineering/Undergraduate (B.A.Sc.) - 2026-06-22 - Active - APSC_V 160 - Introduction to Computation in Engineering Design - 2026-27 Winter Term 1 (UBC-V)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>APSC_V 160 - Introduction to Computation in Engineering Design</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>3</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Graded</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>fake300-301</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Registered</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Graded</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>APSC_V 160-102 - Introduction to Computation in Engineering Design</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Registered</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>Lecture</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>In Person Learning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2026-09-08 - 2026-12-05 | Mon Wed Fri | 10:00 a.m. - 11:00 a.m. | Fake Building (FAKE) | Floor: 1 | Room: 100</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>J. Doe</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2026-12-05</t>
-        </is>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>In Person Learning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-09-08 - 2026-12-03 | Tue Thu | 3:30 p.m. - 5:00 p.m. | UBCV | Wesbrook Building (WESB) | Floor: 1 | Room: 100</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Cristian Sorin Grecu
+Geoffrey Tien</t>
+        </is>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>46363</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Student (00000000) - School of Biomedical Engineering/Undergraduate (B.A.Sc.) - 2026-06-22 - Active - APSC_V 160 - Introduction to Computation in Engineering Design - 2026-27 Winter Term 1 (UBC-V)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>APSC_V 160 - Introduction to Computation in Engineering Design</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Graded</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>APSC_V 160-L1P - Introduction to Computation in Engineering Design</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Registered</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Laboratory</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>In Person Learning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-09-14 - 2026-12-07 | Mon | 8:00 a.m. - 10:00 a.m. | UBCV | Civil and Mechanical Engineering Building (CEME) | Floor: 2 | Room: 2212</t>
+        </is>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>46363</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Student (00000000) - School of Biomedical Engineering/Undergraduate (B.A.Sc.) - 2026-06-22 - Active - MECH_V 260 - Introduction to Mechanics of Materials - 2026-27 Winter Term 1 (UBC-V)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MECH_V 260 - Introduction to Mechanics of Materials</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Graded</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>MECH_V 260-T1B - Introduction to Mechanics of Materials</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Registered</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Discussion</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>In Person Learning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-09-14 - 2026-12-07 | Mon | 2:00 p.m. - 3:00 p.m. | UBCV | Hugh Dempster Pavilion (DMP) | Floor: 3 | Room: 301</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Mona Amer</t>
+        </is>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>46363</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Student (00000000) - School of Biomedical Engineering/Undergraduate (B.A.Sc.) - 2026-06-22 - Active - MECH_V 260 - Introduction to Mechanics of Materials - 2026-27 Winter Term 1 (UBC-V)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MECH_V 260 - Introduction to Mechanics of Materials</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Graded</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>MECH_V 260-102 - Introduction to Mechanics of Materials</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Registered</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Lecture</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>In Person Learning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-09-08 - 2026-12-03 | Tue Thu | 11:00 a.m. - 12:30 p.m. | UBCV | Hugh Dempster Pavilion (DMP) | Floor: 3 | Room: 301</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Mona Amer</t>
+        </is>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>46363</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Student (00000000) - School of Biomedical Engineering/Undergraduate (B.A.Sc.) - 2026-06-22 - Active - BMEG_V 257 - Biomedical Engineering Design I - 2026-27 Winter Term 2 (UBC-V)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BMEG_V 257 - Biomedical Engineering Design I</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Graded</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>BMEG_V 257-201 - Biomedical Engineering Design I</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Registered</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Lecture</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>In Person Learning</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2027-01-05 - 2027-02-11 | Tue Thu | 10:00 a.m. - 11:00 a.m. | UBCV | P. A. Woodward Instructional Resources Centre (IRC) | Floor: G | Room: 5
+2027-02-23 - 2027-04-08 | Tue Thu | 10:00 a.m. - 11:00 a.m. | UBCV | P. A. Woodward Instructional Resources Centre (IRC) | Floor: G | Room: 5</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Calvin Kuo</t>
+        </is>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>46392</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>46485</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Student (00000000) - School of Biomedical Engineering/Undergraduate (B.A.Sc.) - 2026-06-22 - Active - BMEG_V 257 - Biomedical Engineering Design I - 2026-27 Winter Term 2 (UBC-V)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BMEG_V 257 - Biomedical Engineering Design I</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Graded</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>BMEG_V 257-S2A - Biomedical Engineering Design I</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Registered</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Studio</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>In Person Learning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2027-01-05 - 2027-02-11 | Tue Thu | 12:00 p.m. - 2:00 p.m. | UBCV | Gordon B. Shrum Building (SHRM) | Floor: -1 | Room: B1009
+2027-02-23 - 2027-04-08 | Tue Thu | 12:00 p.m. - 2:00 p.m. | UBCV | Gordon B. Shrum Building (SHRM) | Floor: -1 | Room: B1009</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Calvin Kuo</t>
+        </is>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>46392</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>46485</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Student (00000000) - School of Biomedical Engineering/Undergraduate (B.A.Sc.) - 2026-06-22 - Active - BMEG_V 201 - Technical Communication for Biomedical Engineers - 2026-27 Winter Term 2 (UBC-V)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BMEG_V 201 - Technical Communication for Biomedical Engineers</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Graded</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>BMEG_V 201-201 - Technical Communication for Biomedical Engineers</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Registered</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Lecture</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>In Person Learning</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2027-01-06 - 2027-02-12 | Mon Wed Fri | 12:00 p.m. - 1:00 p.m. | UBCV | Pharmaceutical Sciences Building (PHRM) | Floor: 1 | Room: 1101
+2027-02-22 - 2027-04-12 | Mon Wed Fri | 12:00 p.m. - 1:00 p.m. | UBCV | Pharmaceutical Sciences Building (PHRM) | Floor: 1 | Room: 1101</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Sharareh Bayat</t>
+        </is>
+      </c>
+      <c r="N14" s="1" t="n">
+        <v>46393</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>46489</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Student (00000000) - School of Biomedical Engineering/Undergraduate (B.A.Sc.) - 2026-06-22 - Active - ANTH_V 100 - Introduction to Cultural Anthropology - 2026-27 Winter Term 2 (UBC-V)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ANTH_V 100 - Introduction to Cultural Anthropology</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Graded</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ANTH_V 100-A_D4D - Introduction to Cultural Anthropology (A)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Registered</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Discussion</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>In Person Learning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2027-01-08 - 2027-02-12 | Fri | 2:00 p.m. - 3:00 p.m. | UBCV | Buchanan Building (BUCH) | Floor: 2 | Room: B209
+2027-02-26 - 2027-04-09 | Fri | 2:00 p.m. - 3:00 p.m. | UBCV | Buchanan Building (BUCH) | Floor: 2 | Room: B209</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Helena Zeweri</t>
+        </is>
+      </c>
+      <c r="N15" s="1" t="n">
+        <v>46392</v>
+      </c>
+      <c r="O15" s="1" t="n">
+        <v>46489</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Student (00000000) - School of Biomedical Engineering/Undergraduate (B.A.Sc.) - 2026-06-22 - Active - ANTH_V 100 - Introduction to Cultural Anthropology - 2026-27 Winter Term 2 (UBC-V)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ANTH_V 100 - Introduction to Cultural Anthropology</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Graded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ANTH_V 100-A_004 - Introduction to Cultural Anthropology (A)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Registered</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Lecture</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>In Person Learning</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2027-01-06 - 2027-02-10 | Mon Wed | 2:00 p.m. - 3:00 p.m. | UBCV | Irving K. Barber Learning Centre (IBLC) | Floor: 1 | Room: 182
+2027-02-22 - 2027-04-12 | Mon Wed | 2:00 p.m. - 3:00 p.m. | UBCV | Irving K. Barber Learning Centre (IBLC) | Floor: 1 | Room: 182</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Helena Zeweri</t>
+        </is>
+      </c>
+      <c r="N16" s="1" t="n">
+        <v>46392</v>
+      </c>
+      <c r="O16" s="1" t="n">
+        <v>46489</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Student (00000000) - School of Biomedical Engineering/Undergraduate (B.A.Sc.) - 2026-06-22 - Active - AMNE_V 151 - Greek and Roman Mythology - 2026-27 Winter Term 2 (UBC-V)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>AMNE_V 151 - Greek and Roman Mythology</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Graded</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>AMNE_V 151-003 - Greek and Roman Mythology</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Registered</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Lecture</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>In Person Learning</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2027-01-06 - 2027-02-10 | Wed | 5:00 p.m. - 7:00 p.m. | UBCV | Buchanan Building (BUCH) | Floor: 1 | Room: A102
+2027-02-24 - 2027-04-07 | Wed | 5:00 p.m. - 7:00 p.m. | UBCV | Buchanan Building (BUCH) | Floor: 1 | Room: A102</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Antone Minard</t>
+        </is>
+      </c>
+      <c r="N17" s="1" t="n">
+        <v>46393</v>
+      </c>
+      <c r="O17" s="1" t="n">
+        <v>46489</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Student (00000000) - School of Biomedical Engineering/Undergraduate (B.A.Sc.) - 2026-06-22 - Active - AMNE_V 151 - Greek and Roman Mythology - 2026-27 Winter Term 2 (UBC-V)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AMNE_V 151 - Greek and Roman Mythology</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Graded</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>AMNE_V 151-302 - Greek and Roman Mythology</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Registered</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Discussion</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>In Person Learning</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2027-01-08 - 2027-02-12 | Fri | 10:00 a.m. - 11:00 a.m. | UBCV | Buchanan Building (BUCH) | Floor: 3 | Room: B316
+2027-02-26 - 2027-04-09 | Fri | 10:00 a.m. - 11:00 a.m. | UBCV | Buchanan Building (BUCH) | Floor: 3 | Room: B316</t>
+        </is>
+      </c>
+      <c r="N18" s="1" t="n">
+        <v>46393</v>
+      </c>
+      <c r="O18" s="1" t="n">
+        <v>46489</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Student (00000000) - School of Biomedical Engineering/Undergraduate (B.A.Sc.) - 2026-06-22 - Active - BMEG_V 230 - Biomechanics I - 2026-27 Winter Term 1 (UBC-V)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BMEG_V 230 - Biomechanics I</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Graded</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>BMEG_V 230-L1D - Biomechanics I</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Registered</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Laboratory</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>In Person Learning</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-09-15 - 2026-11-24 | Tue (Alternate weeks) | 1:00 p.m. - 3:00 p.m. | UBCV | Gordon B. Shrum Building (SHRM) | Floor: 2 | Room: 2043</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Robyn Newell</t>
+        </is>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="O19" s="1" t="n">
+        <v>46359</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Student (00000000) - School of Biomedical Engineering/Undergraduate (B.A.Sc.) - 2026-06-22 - Active - BMEG_V 230 - Biomechanics I - 2026-27 Winter Term 1 (UBC-V)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BMEG_V 230 - Biomechanics I</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>4</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Graded</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>BMEG_V 230-101 - Biomechanics I</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Registered</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Lecture</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>In Person Learning</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-09-08 - 2026-12-03 | Tue Thu | 9:00 a.m. - 11:00 a.m. | UBCV | Gordon B. Shrum Building (SHRM) | Floor: -1 | Room: B1009</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Robyn Newell</t>
+        </is>
+      </c>
+      <c r="N20" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="O20" s="1" t="n">
+        <v>46359</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Student (00000000) - School of Biomedical Engineering/Undergraduate (B.A.Sc.) - 2026-06-22 - Active - BMEG_V 230 - Biomechanics I - 2026-27 Winter Term 1 (UBC-V)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BMEG_V 230 - Biomechanics I</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>4</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Graded</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>BMEG_V 230-T1D - Biomechanics I</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Registered</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Discussion</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>In Person Learning</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-09-08 - 2026-12-01 | Tue (Alternate weeks) | 1:00 p.m. - 3:00 p.m. | UBCV | Gordon B. Shrum Building (SHRM) | Floor: 2 | Room: 2043</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Robyn Newell</t>
+        </is>
+      </c>
+      <c r="N21" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="O21" s="1" t="n">
+        <v>46359</v>
       </c>
     </row>
   </sheetData>
